--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/OKLAHOMA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/OKLAHOMA_2020.xlsx
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C76">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Praxedis G. Guerero</t>
+          <t>Praxedis G. Guerrero</t>
         </is>
       </c>
       <c r="C91">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C143">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C170">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C210">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C216">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C223">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C471">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C498">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C521">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Totoltepec De Guerero</t>
+          <t>Totoltepec De Guerrero</t>
         </is>
       </c>
       <c r="C582">
